--- a/documentation/Potentiale.xlsx
+++ b/documentation/Potentiale.xlsx
@@ -1,22 +1,57 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="165" windowWidth="14805" windowHeight="7950" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
-    <sheet name="Tabelle2" sheetId="2" r:id="rId2"/>
-    <sheet name="Tabelle3" sheetId="3" r:id="rId3"/>
+    <sheet name="Excel2LaTeX" sheetId="4" state="hidden" r:id="rId1"/>
+    <sheet name="Tabelle1" sheetId="1" r:id="rId2"/>
+    <sheet name="Tabelle2" sheetId="2" r:id="rId3"/>
+    <sheet name="Tabelle3" sheetId="3" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="145621"/>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Autor</author>
+  </authors>
+  <commentList>
+    <comment ref="E66" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Autor:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+dort nur das Dipolmodell?!</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="167">
   <si>
     <t>1CLJ.pm</t>
   </si>
@@ -421,19 +456,136 @@
   </si>
   <si>
     <t>[Hentschke,2007 ; Stockmayer, 1941]</t>
+  </si>
+  <si>
+    <t>Dateiname</t>
+  </si>
+  <si>
+    <t>CAS number</t>
+  </si>
+  <si>
+    <t>Publication</t>
+  </si>
+  <si>
+    <t>Model Type</t>
+  </si>
+  <si>
+    <t>630-08-0</t>
+  </si>
+  <si>
+    <t>\parencite{Stoll2003}</t>
+  </si>
+  <si>
+    <t>2 L.J. Center &amp; Dipole</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>2 L.J. Center &amp; 2 Charges</t>
+  </si>
+  <si>
+    <t>\parencite{Stoll2003} --&gt; ??</t>
+  </si>
+  <si>
+    <t>74-88-4</t>
+  </si>
+  <si>
+    <t>74-87-3</t>
+  </si>
+  <si>
+    <t>74-83-9</t>
+  </si>
+  <si>
+    <t>75-09-2</t>
+  </si>
+  <si>
+    <t>74-95-3</t>
+  </si>
+  <si>
+    <t>75-11-6</t>
+  </si>
+  <si>
+    <t>67-66-3</t>
+  </si>
+  <si>
+    <t>74-97-5</t>
+  </si>
+  <si>
+    <t>RangeAddress</t>
+  </si>
+  <si>
+    <t>Options</t>
+  </si>
+  <si>
+    <t>CellWidth</t>
+  </si>
+  <si>
+    <t>Indent</t>
+  </si>
+  <si>
+    <t>FileName</t>
+  </si>
+  <si>
+    <t>Tabelle1.tex</t>
+  </si>
+  <si>
+    <t>75-25-2</t>
+  </si>
+  <si>
+    <t>75-43-4</t>
+  </si>
+  <si>
+    <t>75-61-6</t>
+  </si>
+  <si>
+    <t>353-59-3</t>
+  </si>
+  <si>
+    <t>75-62-7</t>
+  </si>
+  <si>
+    <t>353-36-6</t>
+  </si>
+  <si>
+    <t>75-34-3</t>
+  </si>
+  <si>
+    <t>79-00-5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -450,7 +602,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -495,15 +647,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -805,709 +967,930 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:D133"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="2" width="19.7109375" bestFit="1" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>153</v>
+      </c>
       <c r="B1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <f>COUNT(Tabelle1!$B$2:$F$135)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B3" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
+      <c r="B2">
+        <v>7</v>
+      </c>
+      <c r="C2">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B24" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B25" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B28" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B29" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B30" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B31" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B32" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B33" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B34" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B35" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B36" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B37" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B38" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B39" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B40" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B41" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B42" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B43" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B44" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B45" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B46" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B47" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B48" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B49" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B50" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B51" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B52" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B53" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B54" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B55" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B56" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B57" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="58" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B58" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="59" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B59" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="60" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B60" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="61" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B61" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="62" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B62" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="63" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B63" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="64" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B64" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B65" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B66" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B67" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B68" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="69" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B69" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="70" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B70" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="71" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B71" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="72" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B72" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="73" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B73" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="74" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B74" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="75" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B75" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="76" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B76" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="77" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B77" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="78" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B78" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="79" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B79" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="80" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B80" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B81" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B82" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B83" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="84" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B84" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="85" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B85" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="86" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B86" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="87" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B87" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="88" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B88" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="89" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B89" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="90" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B90" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="91" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B91" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="92" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B92" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="93" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B93" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="94" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B94" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="95" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B95" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="96" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B96" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="97" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B97" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="98" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B98" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="99" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B99" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="100" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B100" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="101" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B101" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="102" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B102" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="103" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B103" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="104" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B104" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="105" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B105" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="106" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B106" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="107" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B107" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="108" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B108" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="109" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B109" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="110" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B110" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="111" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B111" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="112" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B112" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="113" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B113" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="114" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B114" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="115" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B115" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="116" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B116" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="117" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B117" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="118" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B118" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="119" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B119" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="120" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B120" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="121" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B121" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="122" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B122" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="123" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B123" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="124" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B124" t="s">
-        <v>123</v>
-      </c>
-      <c r="C124" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="125" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B125" t="s">
-        <v>124</v>
-      </c>
-      <c r="C125" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="126" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B126" t="s">
-        <v>125</v>
-      </c>
-      <c r="C126" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="127" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B127" t="s">
-        <v>126</v>
-      </c>
-      <c r="D127" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="128" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B128" t="s">
-        <v>127</v>
-      </c>
-      <c r="C128" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="129" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B129" t="s">
-        <v>128</v>
-      </c>
-      <c r="C129" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="130" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B130" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="131" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B131" t="s">
-        <v>130</v>
-      </c>
-      <c r="C131" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="132" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B132" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="133" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B133" s="2" t="s">
-        <v>132</v>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2" t="s">
+        <v>158</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:F135"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="2" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" customWidth="1"/>
+    <col min="5" max="5" width="33.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:6" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B2" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B5" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" t="s">
+        <v>161</v>
+      </c>
+      <c r="E23" t="s">
+        <v>140</v>
+      </c>
+      <c r="F23" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" t="s">
+        <v>163</v>
+      </c>
+      <c r="E24" t="s">
+        <v>140</v>
+      </c>
+      <c r="F24" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" t="s">
+        <v>162</v>
+      </c>
+      <c r="E25" t="s">
+        <v>140</v>
+      </c>
+      <c r="F25" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" t="s">
+        <v>149</v>
+      </c>
+      <c r="E35" t="s">
+        <v>140</v>
+      </c>
+      <c r="F35" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>36</v>
+      </c>
+      <c r="C39" t="s">
+        <v>152</v>
+      </c>
+      <c r="E39" t="s">
+        <v>140</v>
+      </c>
+      <c r="F39" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>37</v>
+      </c>
+      <c r="C40" t="s">
+        <v>148</v>
+      </c>
+      <c r="E40" t="s">
+        <v>140</v>
+      </c>
+      <c r="F40" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="42" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
+        <v>40</v>
+      </c>
+      <c r="C43" t="s">
+        <v>164</v>
+      </c>
+      <c r="E43" t="s">
+        <v>140</v>
+      </c>
+      <c r="F43" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
+        <v>41</v>
+      </c>
+      <c r="C44" t="s">
+        <v>150</v>
+      </c>
+      <c r="E44" t="s">
+        <v>140</v>
+      </c>
+      <c r="F44" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B45" t="s">
+        <v>42</v>
+      </c>
+      <c r="C45" t="s">
+        <v>147</v>
+      </c>
+      <c r="E45" t="s">
+        <v>140</v>
+      </c>
+      <c r="F45" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="46" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B46" t="s">
+        <v>43</v>
+      </c>
+      <c r="C46" t="s">
+        <v>146</v>
+      </c>
+      <c r="E46" t="s">
+        <v>140</v>
+      </c>
+      <c r="F46" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="47" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B47" t="s">
+        <v>44</v>
+      </c>
+      <c r="C47" t="s">
+        <v>145</v>
+      </c>
+      <c r="E47" t="s">
+        <v>140</v>
+      </c>
+      <c r="F47" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="48" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B48" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B49" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
+        <v>47</v>
+      </c>
+      <c r="C50" t="s">
+        <v>159</v>
+      </c>
+      <c r="E50" t="s">
+        <v>140</v>
+      </c>
+      <c r="F50" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B51" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="53" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B53" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="54" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B55" t="s">
+        <v>52</v>
+      </c>
+      <c r="C55" t="s">
+        <v>166</v>
+      </c>
+      <c r="E55" t="s">
+        <v>140</v>
+      </c>
+      <c r="F55" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B56" t="s">
+        <v>53</v>
+      </c>
+      <c r="C56" t="s">
+        <v>165</v>
+      </c>
+      <c r="E56" t="s">
+        <v>140</v>
+      </c>
+      <c r="F56" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="57" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B57" t="s">
+        <v>54</v>
+      </c>
+      <c r="C57" t="s">
+        <v>151</v>
+      </c>
+      <c r="E57" t="s">
+        <v>140</v>
+      </c>
+      <c r="F57" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B58" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B59" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B60" t="s">
+        <v>57</v>
+      </c>
+      <c r="C60" t="s">
+        <v>160</v>
+      </c>
+      <c r="E60" t="s">
+        <v>140</v>
+      </c>
+      <c r="F60" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B61" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B62" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="63" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B63" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B64" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="65" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B65" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C65" t="s">
+        <v>139</v>
+      </c>
+      <c r="E65" t="s">
+        <v>140</v>
+      </c>
+      <c r="F65" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="66" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B66" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C66" t="s">
+        <v>139</v>
+      </c>
+      <c r="E66" t="s">
+        <v>144</v>
+      </c>
+      <c r="F66" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="67" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B67" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="68" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B68" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="69" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B69" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="70" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B70" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="71" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B71" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="72" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B72" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="73" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B73" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B74" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="75" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B75" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="76" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B76" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="77" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B77" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="78" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B78" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="79" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B79" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="80" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B80" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="81" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B81" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="82" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B82" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="83" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B83" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="84" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B84" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="85" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B85" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="86" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B86" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="87" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B87" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="88" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B88" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="89" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B89" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="90" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B90" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="91" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B91" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="92" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B92" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="93" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B93" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="94" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B94" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="95" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B95" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="96" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B96" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="97" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B97" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="98" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B98" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="99" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B99" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B100" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="101" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B101" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="102" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B102" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="103" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B103" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="104" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B104" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="105" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B105" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="106" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B106" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="107" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B107" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="108" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B108" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="109" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B109" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="110" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B110" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="111" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B111" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="112" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B112" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="113" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B113" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="114" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B114" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="115" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B115" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="116" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B116" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="117" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B117" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="118" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B118" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="119" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B119" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="120" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B120" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="121" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B121" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="122" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B122" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="123" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B123" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="124" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B124" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="125" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B125" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="126" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B126" t="s">
+        <v>123</v>
+      </c>
+      <c r="C126" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="127" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B127" t="s">
+        <v>124</v>
+      </c>
+      <c r="C127" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="128" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B128" t="s">
+        <v>125</v>
+      </c>
+      <c r="C128" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="129" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B129" t="s">
+        <v>126</v>
+      </c>
+      <c r="E129" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="130" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B130" t="s">
+        <v>127</v>
+      </c>
+      <c r="C130" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="131" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B131" t="s">
+        <v>128</v>
+      </c>
+      <c r="C131" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="132" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B132" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="133" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B133" t="s">
+        <v>130</v>
+      </c>
+      <c r="C133" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="134" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B134" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="135" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B135" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1518,4 +1901,13 @@
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>